--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DFS_HRM-2031-0452/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DFS_HRM-2031-0452/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -437,16 +437,6 @@
           <t>Radius</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -454,23 +444,28 @@
           <t>Unit 7</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
       <c r="C2" t="n">
-        <v>16.80507</v>
+        <v>16.89039</v>
       </c>
       <c r="D2" t="n">
-        <v>17.03463</v>
+        <v>16.53045</v>
       </c>
       <c r="E2" t="n">
-        <v>16.74448</v>
+        <v>16.81389</v>
       </c>
       <c r="F2" t="n">
-        <v>42.76506</v>
+        <v>42.79576</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04992</v>
+        <v>0.04993</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82956</v>
+        <v>1.79934</v>
       </c>
     </row>
     <row r="3">
@@ -480,22 +475,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.79839</v>
+        <v>16.91395</v>
       </c>
       <c r="D3" t="n">
-        <v>16.62085</v>
+        <v>16.24803</v>
       </c>
       <c r="E3" t="n">
-        <v>16.6252</v>
+        <v>16.57891</v>
       </c>
       <c r="F3" t="n">
-        <v>41.10511</v>
+        <v>41.98503</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0503</v>
+        <v>0.05125</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83403</v>
+        <v>1.8382</v>
       </c>
     </row>
     <row r="4">
@@ -505,22 +500,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.69754</v>
+        <v>16.95671</v>
       </c>
       <c r="D4" t="n">
-        <v>16.60965</v>
+        <v>16.4639</v>
       </c>
       <c r="E4" t="n">
-        <v>16.8784</v>
+        <v>16.68701</v>
       </c>
       <c r="F4" t="n">
-        <v>42.45129</v>
+        <v>42.45102</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04951</v>
+        <v>0.05082</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82703</v>
+        <v>1.81335</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +525,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.83178</v>
+        <v>17.09262</v>
       </c>
       <c r="D5" t="n">
-        <v>16.90088</v>
+        <v>16.69777</v>
       </c>
       <c r="E5" t="n">
-        <v>16.54134</v>
+        <v>16.80522</v>
       </c>
       <c r="F5" t="n">
-        <v>42.24701</v>
+        <v>42.63924</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05115</v>
+        <v>0.04996</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83122</v>
+        <v>1.79502</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +550,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.74743</v>
+        <v>17.02132</v>
       </c>
       <c r="D6" t="n">
-        <v>16.76956</v>
+        <v>16.73742</v>
       </c>
       <c r="E6" t="n">
-        <v>16.76823</v>
+        <v>16.87778</v>
       </c>
       <c r="F6" t="n">
-        <v>41.96538</v>
+        <v>42.4067</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04986</v>
+        <v>0.05098</v>
       </c>
       <c r="H6" t="n">
-        <v>1.76848</v>
+        <v>1.80254</v>
       </c>
     </row>
     <row r="7">
@@ -580,22 +575,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.71729</v>
+        <v>16.83989</v>
       </c>
       <c r="D7" t="n">
-        <v>16.37263</v>
+        <v>16.38735</v>
       </c>
       <c r="E7" t="n">
-        <v>16.38498</v>
+        <v>16.75264</v>
       </c>
       <c r="F7" t="n">
-        <v>42.61339</v>
+        <v>42.2375</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05092</v>
+        <v>0.04967</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8522</v>
+        <v>1.77643</v>
       </c>
     </row>
     <row r="8">
@@ -605,22 +600,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.7789</v>
+        <v>16.84292</v>
       </c>
       <c r="D8" t="n">
-        <v>16.72916</v>
+        <v>16.5129</v>
       </c>
       <c r="E8" t="n">
-        <v>16.64206</v>
+        <v>16.6417</v>
       </c>
       <c r="F8" t="n">
-        <v>42.64712</v>
+        <v>42.4037</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05065</v>
+        <v>0.05075</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83837</v>
+        <v>1.81543</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +625,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.56553</v>
+        <v>17.09338</v>
       </c>
       <c r="D9" t="n">
-        <v>16.82712</v>
+        <v>16.62181</v>
       </c>
       <c r="E9" t="n">
-        <v>16.54211</v>
+        <v>17.07845</v>
       </c>
       <c r="F9" t="n">
-        <v>41.58522</v>
+        <v>42.84282</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05116</v>
+        <v>0.05011</v>
       </c>
       <c r="H9" t="n">
-        <v>1.80043</v>
+        <v>1.80077</v>
       </c>
     </row>
     <row r="10">
@@ -655,51 +650,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.83975</v>
+        <v>16.86653</v>
       </c>
       <c r="D10" t="n">
-        <v>16.55503</v>
+        <v>16.60608</v>
       </c>
       <c r="E10" t="n">
-        <v>16.79573</v>
+        <v>16.71233</v>
       </c>
       <c r="F10" t="n">
-        <v>42.18513</v>
+        <v>41.88425</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05027</v>
+        <v>0.0498</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8217</v>
+        <v>1.84789</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -713,26 +688,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.03218</v>
+        <v>0.61764</v>
       </c>
       <c r="D12" t="n">
-        <v>16.36372</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.61637</v>
-      </c>
-      <c r="F12" t="n">
-        <v>42.6271</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.05019</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.80269</v>
+        <v>1.08993</v>
       </c>
     </row>
     <row r="13">
@@ -742,22 +705,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.07999</v>
+        <v>0.60453</v>
       </c>
       <c r="D13" t="n">
-        <v>16.81986</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.70532</v>
-      </c>
-      <c r="F13" t="n">
-        <v>42.26994</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.04967</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.84581</v>
+        <v>1.11264</v>
       </c>
     </row>
     <row r="14">
@@ -767,22 +718,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.60368</v>
+        <v>0.60287</v>
       </c>
       <c r="D14" t="n">
-        <v>16.63099</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.90236</v>
-      </c>
-      <c r="F14" t="n">
-        <v>42.50288</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05059</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.80764</v>
+        <v>1.14017</v>
       </c>
     </row>
     <row r="15">
@@ -792,22 +731,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.21228</v>
+        <v>0.60248</v>
       </c>
       <c r="D15" t="n">
-        <v>16.51448</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.62833</v>
-      </c>
-      <c r="F15" t="n">
-        <v>42.0431</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.04958</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.81509</v>
+        <v>1.12369</v>
       </c>
     </row>
     <row r="16">
@@ -817,22 +744,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.79682</v>
+        <v>0.6027</v>
       </c>
       <c r="D16" t="n">
-        <v>16.31115</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.32645</v>
-      </c>
-      <c r="F16" t="n">
-        <v>42.52245</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.05075</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.83448</v>
+        <v>1.11662</v>
       </c>
     </row>
     <row r="17">
@@ -842,22 +757,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.12492</v>
+        <v>0.59109</v>
       </c>
       <c r="D17" t="n">
-        <v>16.5649</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.30369</v>
-      </c>
-      <c r="F17" t="n">
-        <v>42.8818</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.79495</v>
+        <v>1.11181</v>
       </c>
     </row>
     <row r="18">
@@ -867,22 +770,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.28806</v>
+        <v>0.60934</v>
       </c>
       <c r="D18" t="n">
-        <v>16.37788</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.94982</v>
-      </c>
-      <c r="F18" t="n">
-        <v>42.26166</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.05167</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.81168</v>
+        <v>1.10759</v>
       </c>
     </row>
     <row r="19">
@@ -892,22 +783,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.93285</v>
+        <v>0.59485</v>
       </c>
       <c r="D19" t="n">
-        <v>16.36196</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.60959</v>
-      </c>
-      <c r="F19" t="n">
-        <v>42.2557</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05157</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.81787</v>
+        <v>1.11481</v>
       </c>
     </row>
     <row r="20">
@@ -917,22 +796,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.97805</v>
+        <v>0.61364</v>
       </c>
       <c r="D20" t="n">
-        <v>16.35665</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.60193</v>
-      </c>
-      <c r="F20" t="n">
-        <v>42.57017</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.04971</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.8174</v>
+        <v>1.08721</v>
       </c>
     </row>
   </sheetData>
